--- a/example_project/Analysis/MG_motility/all_motility.xlsx
+++ b/example_project/Analysis/MG_motility/all_motility.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,66 +413,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>project tag</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tag folders</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>projection center</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>source image</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>delta t</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Gain</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Loss</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>rel Stable</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>rel Gain</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>rel Loss</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>tor</t>
         </is>
@@ -503,39 +501,49 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>projection_center_23</t>
+          <t>TP000/registered</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ID240103_P17_1/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>t_0-t_1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>blinded</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>438372</v>
-      </c>
-      <c r="G2" t="n">
-        <v>206227</v>
-      </c>
       <c r="H2" t="n">
-        <v>215817</v>
+        <v>601510</v>
       </c>
       <c r="I2" t="n">
-        <v>0.509488433501934</v>
+        <v>208041</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2396828975751265</v>
+        <v>208751</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2508286689229396</v>
+        <v>0.5906990264184888</v>
       </c>
       <c r="L2" t="n">
-        <v>0.490511566498066</v>
+        <v>0.2043018672260292</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.204999106355482</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.4093009735815112</v>
       </c>
     </row>
     <row r="3">
@@ -551,39 +559,49 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>projection_center_23</t>
+          <t>TP000/registered</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ID240103_P17_1/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>t_1-t_2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>blinded</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>433428</v>
-      </c>
-      <c r="G3" t="n">
-        <v>210417</v>
-      </c>
       <c r="H3" t="n">
-        <v>211171</v>
+        <v>598913</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5069238470391197</v>
+        <v>211233</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2460971490591989</v>
+        <v>210638</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2469790039016814</v>
+        <v>0.5867186397905924</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4930761529608803</v>
+        <v>0.2069321227605448</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.2063492374488628</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.4132813602094076</v>
       </c>
     </row>
     <row r="4">
@@ -599,39 +617,49 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>projection_center_23</t>
+          <t>TP000/registered</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ID240103_P17_1/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>t_2-t_3</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>blinded</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>404394</v>
-      </c>
-      <c r="G4" t="n">
-        <v>195940</v>
-      </c>
       <c r="H4" t="n">
-        <v>239451</v>
+        <v>582860</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4815446810790857</v>
+        <v>210705</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2333216239870919</v>
+        <v>227286</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2851336949338223</v>
+        <v>0.5709550169417477</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5184553189209142</v>
+        <v>0.2064013259525631</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2226436571056893</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.4290449830582524</v>
       </c>
     </row>
     <row r="5">
@@ -647,39 +675,49 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>projection_center_23</t>
+          <t>TP000/registered</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ID240103_P17_1/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>t_3-t_4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>blinded</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>392549</v>
-      </c>
-      <c r="G5" t="n">
-        <v>214233</v>
-      </c>
       <c r="H5" t="n">
-        <v>207785</v>
+        <v>573944</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4819112485529122</v>
+        <v>217353</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2630023067470202</v>
+        <v>219621</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2550864447000676</v>
+        <v>0.5677453562009975</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5180887514470879</v>
+        <v>0.2150055691955233</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2172490746034792</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.4322546437990025</v>
       </c>
     </row>
     <row r="6">
@@ -695,39 +733,49 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>projection_center_23</t>
+          <t>TP000/registered</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ID240103_P17_1/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>t_4-t_5</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>blinded</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>393784</v>
-      </c>
-      <c r="G6" t="n">
-        <v>199821</v>
-      </c>
       <c r="H6" t="n">
-        <v>212998</v>
+        <v>574137</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4882005149993243</v>
+        <v>217242</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2477315358360928</v>
+        <v>217160</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2640679491645828</v>
+        <v>0.5692759526404036</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5117994850006756</v>
+        <v>0.2154026765449824</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.215321370814614</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.4307240473595964</v>
       </c>
     </row>
     <row r="7">
@@ -743,39 +791,49 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>projection_center_23</t>
+          <t>TP000/registered</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ID240103_P17_1/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>t_5-t_6</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>blinded</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>377380</v>
-      </c>
-      <c r="G7" t="n">
-        <v>255860</v>
-      </c>
       <c r="H7" t="n">
-        <v>216225</v>
+        <v>563161</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4442560905982</v>
+        <v>238269</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3012013443755776</v>
+        <v>228218</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2545425650262224</v>
+        <v>0.5469451696113623</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5557439094018</v>
+        <v>0.2314082094074868</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2216466209811508</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.4530548303886377</v>
       </c>
     </row>
     <row r="8">
@@ -791,45 +849,55 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>projection_center_23</t>
+          <t>TP000/registered</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ID240103_P17_1/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>t_6-t_7</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>blinded</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>422067</v>
-      </c>
-      <c r="G8" t="n">
-        <v>208346</v>
-      </c>
       <c r="H8" t="n">
-        <v>211173</v>
+        <v>580748</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5015138084521368</v>
+        <v>217223</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2475635288609839</v>
+        <v>220682</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2509226626868793</v>
+        <v>0.5701136697187364</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4984861915478632</v>
+        <v>0.2132453347705254</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2166409955107382</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.4298863302812636</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ID240103_P17_1</t>
+          <t>ID240321_P17_3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -839,45 +907,55 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>projection_center_28</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ID240321_P17_3/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>t_0-t_1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>blinded</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>601510</v>
-      </c>
-      <c r="G9" t="n">
-        <v>208041</v>
-      </c>
       <c r="H9" t="n">
-        <v>208751</v>
+        <v>590436</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5906990264184888</v>
+        <v>201625</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2043018672260292</v>
+        <v>204345</v>
       </c>
       <c r="K9" t="n">
-        <v>0.204999106355482</v>
+        <v>0.5925656810577214</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4093009735815112</v>
+        <v>0.2023522540008792</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2050820649413994</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.4074343189422786</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ID240103_P17_1</t>
+          <t>ID240321_P17_3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -887,45 +965,55 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>projection_center_28</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ID240321_P17_3/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>t_1-t_2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>blinded</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>598913</v>
-      </c>
-      <c r="G10" t="n">
-        <v>211233</v>
-      </c>
       <c r="H10" t="n">
-        <v>210638</v>
+        <v>599762</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5867186397905924</v>
+        <v>198143</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2069321227605448</v>
+        <v>192299</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2063492374488628</v>
+        <v>0.6056953920606258</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4132813602094076</v>
+        <v>0.2001032110554997</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1942013968838744</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.3943046079393741</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ID240103_P17_1</t>
+          <t>ID240321_P17_3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -935,45 +1023,55 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>projection_center_28</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ID240321_P17_3/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>t_2-t_3</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>blinded</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>582860</v>
-      </c>
-      <c r="G11" t="n">
-        <v>210705</v>
-      </c>
       <c r="H11" t="n">
-        <v>227286</v>
+        <v>591965</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5709550169417477</v>
+        <v>200719</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2064013259525631</v>
+        <v>205940</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2226436571056893</v>
+        <v>0.5927806661966867</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4290449830582524</v>
+        <v>0.2009955699041882</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2062237638991252</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.4072193338033134</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ID240103_P17_1</t>
+          <t>ID240321_P17_3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -983,45 +1081,55 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>projection_center_28</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ID240321_P17_3/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>t_3-t_4</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>blinded</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>573944</v>
-      </c>
-      <c r="G12" t="n">
-        <v>217353</v>
-      </c>
       <c r="H12" t="n">
-        <v>219621</v>
+        <v>575536</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5677453562009975</v>
+        <v>206120</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2150055691955233</v>
+        <v>217148</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2172490746034792</v>
+        <v>0.5762251652976961</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4322546437990025</v>
+        <v>0.2063668147103936</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2174080199919103</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.423774834702304</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ID240103_P17_1</t>
+          <t>ID240321_P17_3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1031,45 +1139,55 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>projection_center_28</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ID240321_P17_3/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>t_4-t_5</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>blinded</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>574137</v>
-      </c>
-      <c r="G13" t="n">
-        <v>217242</v>
-      </c>
       <c r="H13" t="n">
-        <v>217160</v>
+        <v>567719</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5692759526404036</v>
+        <v>211163</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2154026765449824</v>
+        <v>213937</v>
       </c>
       <c r="K13" t="n">
-        <v>0.215321370814614</v>
+        <v>0.5718252773164091</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4307240473595964</v>
+        <v>0.2126903292543757</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2154843934292152</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.4281747226835909</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ID240103_P17_1</t>
+          <t>ID240321_P17_3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1079,45 +1197,55 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>projection_center_28</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ID240321_P17_3/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>t_5-t_6</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>blinded</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>563161</v>
-      </c>
-      <c r="G14" t="n">
-        <v>238269</v>
-      </c>
       <c r="H14" t="n">
-        <v>228218</v>
+        <v>569682</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5469451696113623</v>
+        <v>213561</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2314082094074868</v>
+        <v>209200</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2216466209811508</v>
+        <v>0.5740198681435609</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4530548303886377</v>
+        <v>0.215187169439454</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2107929624169852</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.4259801318564391</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ID240103_P17_1</t>
+          <t>ID240321_P17_3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1127,374 +1255,48 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>projection_center_28</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ID240321_P17_3/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>t_6-t_7</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>blinded</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>580748</v>
-      </c>
-      <c r="G15" t="n">
-        <v>217223</v>
-      </c>
       <c r="H15" t="n">
-        <v>220682</v>
+        <v>569655</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5701136697187364</v>
+        <v>212637</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2132453347705254</v>
+        <v>213588</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2166409955107382</v>
+        <v>0.5720116881551994</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4298863302812636</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ID240321_P17_3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>TP000</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>t_0-t_1</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>blinded</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>590436</v>
-      </c>
-      <c r="G16" t="n">
-        <v>201625</v>
-      </c>
-      <c r="H16" t="n">
-        <v>204345</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.5925656810577214</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.2023522540008792</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.2050820649413994</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.4074343189422786</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ID240321_P17_3</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>TP000</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>t_1-t_2</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>blinded</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>599762</v>
-      </c>
-      <c r="G17" t="n">
-        <v>198143</v>
-      </c>
-      <c r="H17" t="n">
-        <v>192299</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.6056953920606258</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.2001032110554997</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.1942013968838744</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.3943046079393741</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ID240321_P17_3</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>TP000</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>t_2-t_3</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>blinded</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>591965</v>
-      </c>
-      <c r="G18" t="n">
-        <v>200719</v>
-      </c>
-      <c r="H18" t="n">
-        <v>205940</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.5927806661966867</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.2009955699041882</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.2062237638991252</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.4072193338033134</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ID240321_P17_3</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>TP000</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>t_3-t_4</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>blinded</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>575536</v>
-      </c>
-      <c r="G19" t="n">
-        <v>206120</v>
-      </c>
-      <c r="H19" t="n">
-        <v>217148</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.5762251652976961</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.2063668147103936</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.2174080199919103</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.423774834702304</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ID240321_P17_3</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>TP000</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>t_4-t_5</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>blinded</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>567719</v>
-      </c>
-      <c r="G20" t="n">
-        <v>211163</v>
-      </c>
-      <c r="H20" t="n">
-        <v>213937</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.5718252773164091</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.2126903292543757</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.2154843934292152</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.4281747226835909</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ID240321_P17_3</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>TP000</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>t_5-t_6</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>blinded</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>569682</v>
-      </c>
-      <c r="G21" t="n">
-        <v>213561</v>
-      </c>
-      <c r="H21" t="n">
-        <v>209200</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.5740198681435609</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.215187169439454</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.2107929624169852</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.4259801318564391</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ID240321_P17_3</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>TP000</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>t_6-t_7</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>blinded</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>569655</v>
-      </c>
-      <c r="G22" t="n">
-        <v>212637</v>
-      </c>
-      <c r="H22" t="n">
-        <v>213588</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.5720116881551994</v>
-      </c>
-      <c r="J22" t="n">
         <v>0.2135166887576816</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M15" t="n">
         <v>0.2144716230871189</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N15" t="n">
         <v>0.4279883118448006</v>
       </c>
     </row>
